--- a/KimTransp.xlsx
+++ b/KimTransp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\5. Projetos TIC - Química - 232\ptic232\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A38BC30-6E9F-4C3B-BA15-DB0BE2D6E2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F054438-3296-4D4D-983A-576B1B4071F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
   </bookViews>
   <sheets>
     <sheet name="Transp" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>Data Pedido</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>Yago Igor Moura</t>
+  </si>
+  <si>
+    <t>Olímpia</t>
   </si>
 </sst>
 </file>
@@ -184,7 +187,7 @@
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +257,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -450,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -489,80 +499,80 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -975,20 +985,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
       <c r="E1" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F1" s="8"/>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
       <c r="J1" s="8" t="s">
         <v>29</v>
       </c>
@@ -997,46 +1007,53 @@
       </c>
     </row>
     <row r="2" spans="2:11" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="27"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="45" t="s">
+        <v>42</v>
+      </c>
       <c r="F2" s="9"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
+      <c r="G2" s="31" t="str">
+        <f ca="1">"Hoje é dia "&amp;TEXT(TODAY(),"dd"" de ""mmmm"" de ""aaaa")</f>
+        <v>Hoje é dia 25 de agosto de 2026</v>
+      </c>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
       <c r="J2" s="10"/>
-      <c r="K2" s="9"/>
+      <c r="K2" s="9">
+        <v>80</v>
+      </c>
     </row>
     <row r="3" spans="2:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="31" t="s">
+      <c r="J3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="31" t="s">
+      <c r="K3" s="19" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1045,23 +1062,31 @@
         <v>46152</v>
       </c>
       <c r="C4" s="12">
-        <f ca="1">B4+(RANDBETWEEN(5,12))</f>
         <v>46164</v>
       </c>
-      <c r="D4" s="13"/>
+      <c r="D4" s="13">
+        <f>C4-B4</f>
+        <v>12</v>
+      </c>
       <c r="E4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="14"/>
+      <c r="F4" s="14" t="str">
+        <f>RIGHT(E4,2)</f>
+        <v>MG</v>
+      </c>
       <c r="G4" s="11">
         <v>1272</v>
       </c>
-      <c r="H4" s="11"/>
+      <c r="H4" s="11">
+        <f>G4/K2</f>
+        <v>15.9</v>
+      </c>
       <c r="I4" s="14" t="s">
         <v>35</v>
       </c>
       <c r="J4" s="15"/>
-      <c r="K4" s="46">
+      <c r="K4" s="14">
         <v>11504.32</v>
       </c>
     </row>
@@ -1070,14 +1095,19 @@
         <v>46120</v>
       </c>
       <c r="C5" s="12">
-        <f t="shared" ref="C5:C12" ca="1" si="0">B5+(RANDBETWEEN(5,12))</f>
-        <v>46129</v>
-      </c>
-      <c r="D5" s="13"/>
+        <v>46127</v>
+      </c>
+      <c r="D5" s="13">
+        <f>C5-B5</f>
+        <v>7</v>
+      </c>
       <c r="E5" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="14"/>
+      <c r="F5" s="14" t="str">
+        <f t="shared" ref="F5:F12" si="0">RIGHT(E5,2)</f>
+        <v>SP</v>
+      </c>
       <c r="G5" s="11">
         <v>702</v>
       </c>
@@ -1086,7 +1116,7 @@
         <v>38</v>
       </c>
       <c r="J5" s="16"/>
-      <c r="K5" s="47">
+      <c r="K5" s="24">
         <v>6742.6</v>
       </c>
     </row>
@@ -1095,14 +1125,19 @@
         <v>46170</v>
       </c>
       <c r="C6" s="12">
-        <f t="shared" ca="1" si="0"/>
         <v>46177</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="13">
+        <f t="shared" ref="D6:D12" si="1">C6-B6</f>
+        <v>7</v>
+      </c>
       <c r="E6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="14"/>
+      <c r="F6" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>PR</v>
+      </c>
       <c r="G6" s="11">
         <v>1486</v>
       </c>
@@ -1111,7 +1146,7 @@
         <v>37</v>
       </c>
       <c r="J6" s="16"/>
-      <c r="K6" s="47">
+      <c r="K6" s="24">
         <v>13292.5</v>
       </c>
     </row>
@@ -1120,14 +1155,19 @@
         <v>46173</v>
       </c>
       <c r="C7" s="12">
-        <f t="shared" ca="1" si="0"/>
         <v>46185</v>
       </c>
-      <c r="D7" s="13"/>
+      <c r="D7" s="13">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
       <c r="E7" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="14"/>
+      <c r="F7" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>GO</v>
+      </c>
       <c r="G7" s="11">
         <v>1028</v>
       </c>
@@ -1136,7 +1176,7 @@
         <v>39</v>
       </c>
       <c r="J7" s="16"/>
-      <c r="K7" s="47">
+      <c r="K7" s="24">
         <v>9465.9699999999993</v>
       </c>
     </row>
@@ -1145,14 +1185,19 @@
         <v>46072</v>
       </c>
       <c r="C8" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>46082</v>
-      </c>
-      <c r="D8" s="13"/>
+        <v>46083</v>
+      </c>
+      <c r="D8" s="13">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
       <c r="E8" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="14"/>
+      <c r="F8" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>RS</v>
+      </c>
       <c r="G8" s="11">
         <v>3076</v>
       </c>
@@ -1161,7 +1206,7 @@
         <v>36</v>
       </c>
       <c r="J8" s="16"/>
-      <c r="K8" s="47">
+      <c r="K8" s="24">
         <v>26574.76</v>
       </c>
     </row>
@@ -1170,14 +1215,19 @@
         <v>46091</v>
       </c>
       <c r="C9" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>46103</v>
-      </c>
-      <c r="D9" s="13"/>
+        <v>46101</v>
+      </c>
+      <c r="D9" s="13">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
       <c r="E9" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="14"/>
+      <c r="F9" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>PE</v>
+      </c>
       <c r="G9" s="11">
         <v>5231</v>
       </c>
@@ -1186,7 +1236,7 @@
         <v>40</v>
       </c>
       <c r="J9" s="16"/>
-      <c r="K9" s="47">
+      <c r="K9" s="24">
         <v>44577.41</v>
       </c>
     </row>
@@ -1195,14 +1245,19 @@
         <v>46075</v>
       </c>
       <c r="C10" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>46086</v>
-      </c>
-      <c r="D10" s="13"/>
+        <v>46080</v>
+      </c>
+      <c r="D10" s="13">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
       <c r="E10" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="14"/>
+      <c r="F10" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>RJ</v>
+      </c>
       <c r="G10" s="11">
         <v>1701</v>
       </c>
@@ -1211,7 +1266,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="16"/>
-      <c r="K10" s="47">
+      <c r="K10" s="24">
         <v>15088.51</v>
       </c>
     </row>
@@ -1220,14 +1275,19 @@
         <v>46068</v>
       </c>
       <c r="C11" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>46080</v>
-      </c>
-      <c r="D11" s="13"/>
+        <v>46078</v>
+      </c>
+      <c r="D11" s="13">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
       <c r="E11" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="14"/>
+      <c r="F11" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>BA</v>
+      </c>
       <c r="G11" s="11">
         <v>3882</v>
       </c>
@@ -1236,7 +1296,7 @@
         <v>35</v>
       </c>
       <c r="J11" s="16"/>
-      <c r="K11" s="47">
+      <c r="K11" s="24">
         <v>33308.019999999997</v>
       </c>
     </row>
@@ -1245,14 +1305,19 @@
         <v>46186</v>
       </c>
       <c r="C12" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>46196</v>
-      </c>
-      <c r="D12" s="13"/>
+        <v>46198</v>
+      </c>
+      <c r="D12" s="13">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
       <c r="E12" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="14"/>
+      <c r="F12" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>SP</v>
+      </c>
       <c r="G12" s="11">
         <v>916</v>
       </c>
@@ -1261,7 +1326,7 @@
         <v>39</v>
       </c>
       <c r="J12" s="16"/>
-      <c r="K12" s="47">
+      <c r="K12" s="24">
         <v>8530.33</v>
       </c>
     </row>
@@ -1270,107 +1335,105 @@
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="E14" s="41" t="s">
+      <c r="C14" s="36"/>
+      <c r="E14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="28"/>
-      <c r="H14" s="44" t="s">
+      <c r="F14" s="18"/>
+      <c r="H14" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="45"/>
+      <c r="I14" s="34"/>
     </row>
     <row r="15" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="29"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="19"/>
+      <c r="F15" s="17"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="26"/>
     </row>
     <row r="16" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="E16" s="43" t="s">
+      <c r="C16" s="38"/>
+      <c r="E16" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="28"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
+      <c r="F16" s="18"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
     </row>
     <row r="17" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="18"/>
-      <c r="C17" s="19"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
       <c r="E17" s="6"/>
       <c r="F17" s="17"/>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="45"/>
+      <c r="I17" s="34"/>
     </row>
     <row r="18" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="19"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="26"/>
     </row>
     <row r="19" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="E19" s="41" t="s">
+      <c r="C19" s="44"/>
+      <c r="E19" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="28"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
+      <c r="F19" s="18"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
     </row>
     <row r="20" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="36"/>
+      <c r="C20" s="38"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="29"/>
-      <c r="H20" s="44" t="s">
+      <c r="F20" s="17"/>
+      <c r="H20" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="45"/>
+      <c r="I20" s="34"/>
     </row>
     <row r="21" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="25"/>
-      <c r="C21" s="26"/>
-      <c r="F21" s="30"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="19"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="26"/>
     </row>
     <row r="22" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="E22" s="41" t="s">
+      <c r="C22" s="38"/>
+      <c r="E22" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="28"/>
+      <c r="F22" s="18"/>
     </row>
     <row r="23" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="25"/>
-      <c r="C23" s="26"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="30"/>
     </row>
     <row r="24" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="29"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="42"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="17"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26"/>
@@ -1404,9 +1467,12 @@
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{E839BB19-5F09-4525-9529-897BA60ABD8A}">
       <formula1>"Guariroba,Jurupema,Taquaritinga,Vila Negri"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{E8739A41-89D9-4A5B-8841-8BC2682A826B}">
+      <formula1>"Baguaçu,Cajobi,Guaraci,Olímpia,Severínia"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/KimTransp.xlsx
+++ b/KimTransp.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\5. Projetos TIC - Química - 232\ptic232\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F054438-3296-4D4D-983A-576B1B4071F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD79B81B-5232-466F-874C-638EC788AFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Transp" sheetId="1" r:id="rId1"/>
+    <sheet name="Introdução" sheetId="2" r:id="rId1"/>
+    <sheet name="Tabela_periódica" sheetId="3" r:id="rId2"/>
+    <sheet name="Transp" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Transp!$B$3:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Transp!$B$3:$I$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
   <si>
     <t>Data Pedido</t>
   </si>
@@ -176,6 +178,159 @@
   </si>
   <si>
     <t>Olímpia</t>
+  </si>
+  <si>
+    <t>Operadores de cálculo e ordem de execução</t>
+  </si>
+  <si>
+    <t>Operador aritmético</t>
+  </si>
+  <si>
+    <t>Significado</t>
+  </si>
+  <si>
+    <t>Exemplo</t>
+  </si>
+  <si>
+    <t>Operador de comparação</t>
+  </si>
+  <si>
+    <t>+ (sinal de adição)</t>
+  </si>
+  <si>
+    <t>Adição</t>
+  </si>
+  <si>
+    <t>=A2+B2</t>
+  </si>
+  <si>
+    <t>=  (sinal de igual)</t>
+  </si>
+  <si>
+    <t>Igual a</t>
+  </si>
+  <si>
+    <t>=E2=F2</t>
+  </si>
+  <si>
+    <t>- (sinal de subtração)</t>
+  </si>
+  <si>
+    <t>Subtração</t>
+  </si>
+  <si>
+    <t>=A2-B2</t>
+  </si>
+  <si>
+    <t>&gt;  (sinal de maior)</t>
+  </si>
+  <si>
+    <t>Maior que</t>
+  </si>
+  <si>
+    <t>=E2&gt;F2</t>
+  </si>
+  <si>
+    <t>* (asterisco)</t>
+  </si>
+  <si>
+    <t>Multiplicação</t>
+  </si>
+  <si>
+    <t>=A2*B2</t>
+  </si>
+  <si>
+    <t>&lt;  (sinal de menor)</t>
+  </si>
+  <si>
+    <t>Menor que</t>
+  </si>
+  <si>
+    <t>=E2&lt;F2</t>
+  </si>
+  <si>
+    <t>/ (barra)</t>
+  </si>
+  <si>
+    <t>Divisão</t>
+  </si>
+  <si>
+    <t>=A2/B2</t>
+  </si>
+  <si>
+    <t>&gt;=  (sinal de maior ou igual)</t>
+  </si>
+  <si>
+    <t>Maior ou igual a</t>
+  </si>
+  <si>
+    <t>=E2&gt;=F2</t>
+  </si>
+  <si>
+    <t>% (símbolo de percentagem)</t>
+  </si>
+  <si>
+    <t>Percentagem</t>
+  </si>
+  <si>
+    <t>=A2*0,5</t>
+  </si>
+  <si>
+    <t>&lt;=  (sinal de menor ou igual)</t>
+  </si>
+  <si>
+    <t>Menor ou igual a</t>
+  </si>
+  <si>
+    <t>=E2&lt;=F2</t>
+  </si>
+  <si>
+    <t>^ (acento circunflexo)</t>
+  </si>
+  <si>
+    <t>Exponenciação</t>
+  </si>
+  <si>
+    <t>=A2^B2</t>
+  </si>
+  <si>
+    <t>&lt;&gt;  (sinal de diferente)</t>
+  </si>
+  <si>
+    <t>Diferente de</t>
+  </si>
+  <si>
+    <t>=E2&lt;&gt;F2</t>
+  </si>
+  <si>
+    <t>Operadores de referência</t>
+  </si>
+  <si>
+    <t>: (dois pontos)</t>
+  </si>
+  <si>
+    <t>Operador de intervalo, que produz uma referência a todas as células entre duas referências, incluindo as duas referências. Sentido de "até"</t>
+  </si>
+  <si>
+    <t>=A2:G2</t>
+  </si>
+  <si>
+    <t>; (ponto e vírgula)</t>
+  </si>
+  <si>
+    <t>Operador de União que combina várias referências numa só. Sentido de "e"</t>
+  </si>
+  <si>
+    <t>=SOMA(A2;B2;E2;F2;)</t>
+  </si>
+  <si>
+    <t>(espaço)</t>
+  </si>
+  <si>
+    <t>Operador de interseção, que produz no referência a células comuns às duas referências.</t>
+  </si>
+  <si>
+    <t>=A2:B2 E2:F2)</t>
   </si>
 </sst>
 </file>
@@ -187,7 +342,7 @@
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,8 +419,28 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -284,8 +459,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -455,12 +636,147 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -487,17 +803,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -509,7 +816,33 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -546,32 +879,89 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -597,6 +987,239 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>610298</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>500122</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EC3182C-28A0-4D42-8A1F-C7EAB72DDC20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="5153025"/>
+          <a:ext cx="6944423" cy="2862322"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28576</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>509731</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="Resultado de imagem para cursores do excel">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AD2A84D-7E9F-4E50-BEF2-ED0F047B260A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7058025" y="5133976"/>
+          <a:ext cx="5981700" cy="2890980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>285750</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>695325</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>457200</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2049" name="Object 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2049"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D69B7A8A-44AF-485B-91E0-3058B0307A3E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>563537</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ED0B6B3-48BA-4DEB-9FB2-765907ADD2D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12755537" cy="8839200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -967,6 +1590,318 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D651C4A4-6B52-42EC-9A65-F3746A005D4A}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="30.42578125" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" customWidth="1"/>
+    <col min="5" max="7" width="29.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+    </row>
+    <row r="3" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="46"/>
+      <c r="E3" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="52" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="46"/>
+      <c r="E4" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="46"/>
+      <c r="E5" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="46"/>
+      <c r="E6" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="46"/>
+      <c r="E7" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="55" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="46"/>
+      <c r="E8" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="46"/>
+      <c r="E9" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="57" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="59"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="60"/>
+    </row>
+    <row r="11" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="61"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="52" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="63"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="65" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="63"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="65" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="66"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="68" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="59"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="60"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="60"/>
+    </row>
+    <row r="21" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="60"/>
+    </row>
+    <row r="24" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Excel.Sheet.8" shapeId="2049" r:id="rId3">
+          <objectPr defaultSize="0" autoPict="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>161925</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>285750</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>695325</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>457200</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Excel.Sheet.8" shapeId="2049" r:id="rId3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E8D3F38-01B0-42F0-B78F-841D7CD788A2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84977A75-63E6-465B-876C-1551E84420CF}">
   <dimension ref="B1:K33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -985,20 +1920,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
       <c r="E1" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F1" s="8"/>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="8" t="s">
         <v>29</v>
       </c>
@@ -1007,104 +1942,101 @@
       </c>
     </row>
     <row r="2" spans="2:11" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="45" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="19" t="s">
         <v>42</v>
       </c>
       <c r="F2" s="9"/>
-      <c r="G2" s="31" t="str">
+      <c r="G2" s="34" t="str">
         <f ca="1">"Hoje é dia "&amp;TEXT(TODAY(),"dd"" de ""mmmm"" de ""aaaa")</f>
-        <v>Hoje é dia 25 de agosto de 2026</v>
-      </c>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
+        <v>Hoje é dia 01 de setembro de 2026</v>
+      </c>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
       <c r="J2" s="10"/>
       <c r="K2" s="9">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="12">
+      <c r="B4" s="40">
         <v>46152</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="40">
         <v>46164</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="11">
         <f>C4-B4</f>
         <v>12</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="14" t="str">
+      <c r="F4" s="11" t="str">
         <f>RIGHT(E4,2)</f>
         <v>MG</v>
       </c>
       <c r="G4" s="11">
         <v>1272</v>
       </c>
-      <c r="H4" s="11">
-        <f>G4/K2</f>
-        <v>15.9</v>
-      </c>
-      <c r="I4" s="14" t="s">
+      <c r="H4" s="11"/>
+      <c r="I4" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="14">
+      <c r="J4" s="42"/>
+      <c r="K4" s="43">
         <v>11504.32</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="12">
+      <c r="B5" s="40">
         <v>46120</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="40">
         <v>46127</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="11">
         <f>C5-B5</f>
         <v>7</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="14" t="str">
+      <c r="F5" s="11" t="str">
         <f t="shared" ref="F5:F12" si="0">RIGHT(E5,2)</f>
         <v>SP</v>
       </c>
@@ -1112,29 +2044,29 @@
         <v>702</v>
       </c>
       <c r="H5" s="11"/>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="24">
+      <c r="J5" s="43"/>
+      <c r="K5" s="43">
         <v>6742.6</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="12">
+      <c r="B6" s="40">
         <v>46170</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="40">
         <v>46177</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="11">
         <f t="shared" ref="D6:D12" si="1">C6-B6</f>
         <v>7</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="14" t="str">
+      <c r="F6" s="11" t="str">
         <f t="shared" si="0"/>
         <v>PR</v>
       </c>
@@ -1142,29 +2074,29 @@
         <v>1486</v>
       </c>
       <c r="H6" s="11"/>
-      <c r="I6" t="s">
+      <c r="I6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="24">
+      <c r="J6" s="43"/>
+      <c r="K6" s="43">
         <v>13292.5</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="12">
+      <c r="B7" s="40">
         <v>46173</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="40">
         <v>46185</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="14" t="str">
+      <c r="F7" s="11" t="str">
         <f t="shared" si="0"/>
         <v>GO</v>
       </c>
@@ -1172,29 +2104,29 @@
         <v>1028</v>
       </c>
       <c r="H7" s="11"/>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="24">
+      <c r="J7" s="43"/>
+      <c r="K7" s="43">
         <v>9465.9699999999993</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="12">
+      <c r="B8" s="40">
         <v>46072</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="40">
         <v>46083</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="11">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="14" t="str">
+      <c r="F8" s="11" t="str">
         <f t="shared" si="0"/>
         <v>RS</v>
       </c>
@@ -1202,29 +2134,29 @@
         <v>3076</v>
       </c>
       <c r="H8" s="11"/>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="24">
+      <c r="J8" s="43"/>
+      <c r="K8" s="43">
         <v>26574.76</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="12">
+      <c r="B9" s="40">
         <v>46091</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="40">
         <v>46101</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="11">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="14" t="str">
+      <c r="F9" s="11" t="str">
         <f t="shared" si="0"/>
         <v>PE</v>
       </c>
@@ -1232,29 +2164,29 @@
         <v>5231</v>
       </c>
       <c r="H9" s="11"/>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="24">
+      <c r="J9" s="43"/>
+      <c r="K9" s="43">
         <v>44577.41</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="12">
+      <c r="B10" s="40">
         <v>46075</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="40">
         <v>46080</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="11">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="14" t="str">
+      <c r="F10" s="11" t="str">
         <f t="shared" si="0"/>
         <v>RJ</v>
       </c>
@@ -1262,29 +2194,29 @@
         <v>1701</v>
       </c>
       <c r="H10" s="11"/>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="J10" s="16"/>
-      <c r="K10" s="24">
+      <c r="J10" s="43"/>
+      <c r="K10" s="43">
         <v>15088.51</v>
       </c>
     </row>
     <row r="11" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="12">
+      <c r="B11" s="40">
         <v>46068</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="40">
         <v>46078</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="11">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="14" t="str">
+      <c r="F11" s="11" t="str">
         <f t="shared" si="0"/>
         <v>BA</v>
       </c>
@@ -1292,29 +2224,29 @@
         <v>3882</v>
       </c>
       <c r="H11" s="11"/>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="24">
+      <c r="J11" s="43"/>
+      <c r="K11" s="43">
         <v>33308.019999999997</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="12">
+      <c r="B12" s="40">
         <v>46186</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="40">
         <v>46198</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="14" t="str">
+      <c r="F12" s="11" t="str">
         <f t="shared" si="0"/>
         <v>SP</v>
       </c>
@@ -1322,11 +2254,11 @@
         <v>916</v>
       </c>
       <c r="H12" s="11"/>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="24">
+      <c r="J12" s="43"/>
+      <c r="K12" s="43">
         <v>8530.33</v>
       </c>
     </row>
@@ -1335,105 +2267,105 @@
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="E14" s="21" t="s">
+      <c r="C14" s="39"/>
+      <c r="E14" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="H14" s="33" t="s">
+      <c r="F14" s="13"/>
+      <c r="H14" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="34"/>
+      <c r="I14" s="37"/>
     </row>
     <row r="15" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="27"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="17"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="26"/>
+      <c r="F15" s="12"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="29"/>
     </row>
     <row r="16" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="E16" s="23" t="s">
+      <c r="C16" s="25"/>
+      <c r="E16" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="18"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
+      <c r="F16" s="13"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
     </row>
     <row r="17" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="17"/>
-      <c r="H17" s="33" t="s">
+      <c r="F17" s="12"/>
+      <c r="H17" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="34"/>
+      <c r="I17" s="37"/>
     </row>
     <row r="18" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="26"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="29"/>
     </row>
     <row r="19" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="E19" s="21" t="s">
+      <c r="C19" s="23"/>
+      <c r="E19" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="18"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
+      <c r="F19" s="13"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
     </row>
     <row r="20" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="38"/>
+      <c r="C20" s="25"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="17"/>
-      <c r="H20" s="33" t="s">
+      <c r="F20" s="12"/>
+      <c r="H20" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="34"/>
+      <c r="I20" s="37"/>
     </row>
     <row r="21" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="27"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="29"/>
     </row>
     <row r="22" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="38"/>
-      <c r="E22" s="21" t="s">
+      <c r="C22" s="25"/>
+      <c r="E22" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="18"/>
+      <c r="F22" s="13"/>
     </row>
     <row r="23" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="27"/>
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="41"/>
-      <c r="C24" s="42"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="17"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="21"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="12"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26"/>
@@ -1444,12 +2376,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="H19:I19"/>
@@ -1466,6 +2392,12 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{E839BB19-5F09-4525-9529-897BA60ABD8A}">

--- a/KimTransp.xlsx
+++ b/KimTransp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\5. Projetos TIC - Química - 232\ptic232\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD79B81B-5232-466F-874C-638EC788AFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19863E5C-9E79-4EAF-BE1E-E89102311132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{DF3537CB-6E0A-4E7C-ABFB-B677C0E8847D}"/>
   </bookViews>
   <sheets>
     <sheet name="Introdução" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
   <si>
     <t>Data Pedido</t>
   </si>
@@ -144,9 +144,6 @@
     <t>Data atual</t>
   </si>
   <si>
-    <t>Velocidade média</t>
-  </si>
-  <si>
     <t>Custos totais</t>
   </si>
   <si>
@@ -331,6 +328,15 @@
   </si>
   <si>
     <t>=A2:B2 E2:F2)</t>
+  </si>
+  <si>
+    <t>Velocidade máxima</t>
+  </si>
+  <si>
+    <t>Lucro</t>
+  </si>
+  <si>
+    <t>km/h</t>
   </si>
 </sst>
 </file>
@@ -466,7 +472,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -771,12 +777,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFC000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFC000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -799,9 +830,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -819,66 +847,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -892,12 +860,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -942,20 +904,11 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -963,10 +916,107 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -990,13 +1040,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>610298</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>500122</xdr:rowOff>
@@ -1042,13 +1092,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>28576</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>509731</xdr:rowOff>
@@ -1110,13 +1160,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>5</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>161925</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>285750</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>6</xdr:col>
+          <xdr:col>7</xdr:col>
           <xdr:colOff>695325</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>457200</xdr:rowOff>
@@ -1129,7 +1179,7 @@
                   <a14:compatExt spid="_x0000_s2049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D69B7A8A-44AF-485B-91E0-3058B0307A3E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1591,272 +1641,273 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D651C4A4-6B52-42EC-9A65-F3746A005D4A}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="B1:H26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="30.42578125" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" customWidth="1"/>
-    <col min="5" max="7" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" customWidth="1"/>
+    <col min="2" max="4" width="30.42578125" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" customWidth="1"/>
+    <col min="6" max="8" width="29.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+    </row>
+    <row r="2" spans="2:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+    </row>
+    <row r="3" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-    </row>
-    <row r="3" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="C3" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="D3" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="E3" s="23"/>
+      <c r="F3" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="50" t="s">
+      <c r="G3" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="C4" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="23"/>
+      <c r="F4" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="23"/>
+      <c r="F5" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="23"/>
+      <c r="F6" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="23"/>
+      <c r="F7" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="23"/>
+      <c r="F8" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="23"/>
+      <c r="F9" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="37"/>
+    </row>
+    <row r="11" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="64"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="52" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="55" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" s="55" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="46"/>
-      <c r="E6" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="55" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="55" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="46"/>
-      <c r="E8" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="54" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="55" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="58" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="46"/>
-      <c r="E9" s="56" t="s">
-        <v>81</v>
-      </c>
-      <c r="F9" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="59"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="60"/>
-    </row>
-    <row r="11" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    </row>
+    <row r="12" spans="2:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="52" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="53" t="s">
+      <c r="C12" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="63" t="s">
+      <c r="D12" s="65"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="63"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="65" t="s">
+    </row>
+    <row r="13" spans="2:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="30" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
+      <c r="C13" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="63" t="s">
+      <c r="D13" s="65"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="63"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="65" t="s">
+    </row>
+    <row r="14" spans="2:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="33" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="56" t="s">
+      <c r="C14" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="66" t="s">
+      <c r="D14" s="61"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="66"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="68" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="59"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="60"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="60"/>
-    </row>
-    <row r="21" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="60"/>
-    </row>
-    <row r="24" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="15" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="37"/>
+    </row>
+    <row r="21" spans="2:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="37"/>
+    </row>
+    <row r="24" spans="2:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -1868,13 +1919,13 @@
           <objectPr defaultSize="0" autoPict="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>5</xdr:col>
+                <xdr:col>6</xdr:col>
                 <xdr:colOff>161925</xdr:colOff>
                 <xdr:row>9</xdr:row>
                 <xdr:rowOff>285750</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>6</xdr:col>
+                <xdr:col>7</xdr:col>
                 <xdr:colOff>695325</xdr:colOff>
                 <xdr:row>13</xdr:row>
                 <xdr:rowOff>457200</xdr:rowOff>
@@ -1903,7 +1954,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84977A75-63E6-465B-876C-1551E84420CF}">
-  <dimension ref="B1:K33"/>
+  <dimension ref="B1:L33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1913,459 +1964,560 @@
     <col min="5" max="5" width="21.85546875" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" customWidth="1"/>
     <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="40.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B1" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
       <c r="E1" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F1" s="8"/>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="8" t="s">
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="2:11" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="19" t="s">
-        <v>42</v>
+      <c r="K1" s="69" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="69"/>
+    </row>
+    <row r="2" spans="2:12" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="18" t="s">
+        <v>41</v>
       </c>
       <c r="F2" s="9"/>
-      <c r="G2" s="34" t="str">
-        <f ca="1">"Hoje é dia "&amp;TEXT(TODAY(),"dd"" de ""mmmm"" de ""aaaa")</f>
-        <v>Hoje é dia 01 de setembro de 2026</v>
-      </c>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="9">
+      <c r="G2" s="72" t="str">
+        <f ca="1">"Hoje é "&amp;TEXT(TODAY(),"dddd"", dia ""dd"" de ""mmmm"" de ""aaaa")</f>
+        <v>Hoje é quarta-feira, dia 02 de setembro de 2026</v>
+      </c>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="70" t="str">
+        <f ca="1">TEXT(NOW(),"hh:mm:ss")</f>
+        <v>18:42:34</v>
+      </c>
+      <c r="K2" s="10">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="2:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="14" t="s">
+      <c r="L2" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="67" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="40">
+      <c r="L3" s="67" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="19">
         <v>46152</v>
       </c>
-      <c r="C4" s="40">
+      <c r="C4" s="19">
         <v>46164</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <f>C4-B4</f>
         <v>12</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="11" t="str">
+      <c r="F4" s="10" t="str">
         <f>RIGHT(E4,2)</f>
         <v>MG</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <v>1272</v>
       </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="42"/>
-      <c r="K4" s="43">
+      <c r="H4" s="10" t="str">
+        <f>TEXT((G4/$K$2)/24,"dd"" dia, ""hh"" horas, ""mm"" minutos, ""ss"" segundos""")</f>
+        <v>00 dia, 15 horas, 54 minutos, 00 segundos</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="21">
+        <f>IF(G4&gt;=1000,K4*35%,K4*45%)</f>
+        <v>4026.5119999999997</v>
+      </c>
+      <c r="K4" s="22">
         <v>11504.32</v>
       </c>
-    </row>
-    <row r="5" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="40">
+      <c r="L4" s="74">
+        <f>1-J4/K4</f>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="19">
         <v>46120</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="19">
         <v>46127</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <f>C5-B5</f>
         <v>7</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="11" t="str">
+      <c r="F5" s="10" t="str">
         <f t="shared" ref="F5:F12" si="0">RIGHT(E5,2)</f>
         <v>SP</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <v>702</v>
       </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43">
+      <c r="H5" s="10" t="str">
+        <f t="shared" ref="H5:H12" si="1">TEXT((G5/$K$2)/24,"dd"" dia, ""hh"" horas, ""mm"" minutos, ""ss"" segundos""")</f>
+        <v>00 dia, 08 horas, 46 minutos, 30 segundos</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="21">
+        <f t="shared" ref="J5:J12" si="2">IF(G5&gt;=1000,K5*35%,K5*45%)</f>
+        <v>3034.17</v>
+      </c>
+      <c r="K5" s="22">
         <v>6742.6</v>
       </c>
-    </row>
-    <row r="6" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="40">
+      <c r="L5" s="75">
+        <f t="shared" ref="L5:L12" si="3">1-J5/K5</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="19">
         <v>46170</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="19">
         <v>46177</v>
       </c>
-      <c r="D6" s="11">
-        <f t="shared" ref="D6:D12" si="1">C6-B6</f>
+      <c r="D6" s="10">
+        <f t="shared" ref="D6:D12" si="4">C6-B6</f>
         <v>7</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="11" t="str">
+      <c r="F6" s="10" t="str">
         <f t="shared" si="0"/>
         <v>PR</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <v>1486</v>
       </c>
-      <c r="H6" s="11"/>
+      <c r="H6" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>00 dia, 18 horas, 34 minutos, 30 segundos</v>
+      </c>
       <c r="I6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43">
+        <v>36</v>
+      </c>
+      <c r="J6" s="21">
+        <f>IF(G6&gt;=1000,K6*35%,K6*45%)</f>
+        <v>4652.375</v>
+      </c>
+      <c r="K6" s="22">
         <v>13292.5</v>
       </c>
-    </row>
-    <row r="7" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="40">
+      <c r="L6" s="74">
+        <f t="shared" si="3"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="19">
         <v>46173</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="19">
         <v>46185</v>
       </c>
-      <c r="D7" s="11">
-        <f t="shared" si="1"/>
+      <c r="D7" s="10">
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="11" t="str">
+      <c r="F7" s="10" t="str">
         <f t="shared" si="0"/>
         <v>GO</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <v>1028</v>
       </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43">
+      <c r="H7" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>00 dia, 12 horas, 51 minutos, 00 segundos</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="21">
+        <f t="shared" si="2"/>
+        <v>3313.0894999999996</v>
+      </c>
+      <c r="K7" s="22">
         <v>9465.9699999999993</v>
       </c>
-    </row>
-    <row r="8" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="40">
+      <c r="L7" s="74">
+        <f t="shared" si="3"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="19">
         <v>46072</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="19">
         <v>46083</v>
       </c>
-      <c r="D8" s="11">
-        <f t="shared" si="1"/>
+      <c r="D8" s="10">
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="11" t="str">
+      <c r="F8" s="10" t="str">
         <f t="shared" si="0"/>
         <v>RS</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <v>3076</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43">
+      <c r="H8" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>01 dia, 14 horas, 27 minutos, 00 segundos</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="21">
+        <f t="shared" si="2"/>
+        <v>9301.1659999999993</v>
+      </c>
+      <c r="K8" s="22">
         <v>26574.76</v>
       </c>
-    </row>
-    <row r="9" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="40">
+      <c r="L8" s="74">
+        <f t="shared" si="3"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="19">
         <v>46091</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="19">
         <v>46101</v>
       </c>
-      <c r="D9" s="11">
-        <f t="shared" si="1"/>
+      <c r="D9" s="10">
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="11" t="str">
+      <c r="F9" s="10" t="str">
         <f t="shared" si="0"/>
         <v>PE</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <v>5231</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43">
+      <c r="H9" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>02 dia, 17 horas, 23 minutos, 15 segundos</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="21">
+        <f t="shared" si="2"/>
+        <v>15602.093500000001</v>
+      </c>
+      <c r="K9" s="22">
         <v>44577.41</v>
       </c>
-    </row>
-    <row r="10" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="40">
+      <c r="L9" s="74">
+        <f t="shared" si="3"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="19">
         <v>46075</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="19">
         <v>46080</v>
       </c>
-      <c r="D10" s="11">
-        <f t="shared" si="1"/>
+      <c r="D10" s="10">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="11" t="str">
+      <c r="F10" s="10" t="str">
         <f t="shared" si="0"/>
         <v>RJ</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <v>1701</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43">
+      <c r="H10" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>00 dia, 21 horas, 15 minutos, 45 segundos</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="21">
+        <f t="shared" si="2"/>
+        <v>5280.9785000000002</v>
+      </c>
+      <c r="K10" s="22">
         <v>15088.51</v>
       </c>
-    </row>
-    <row r="11" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="40">
+      <c r="L10" s="74">
+        <f t="shared" si="3"/>
+        <v>0.64999999999999991</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="19">
         <v>46068</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="19">
         <v>46078</v>
       </c>
-      <c r="D11" s="11">
-        <f t="shared" si="1"/>
+      <c r="D11" s="10">
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="11" t="str">
+      <c r="F11" s="10" t="str">
         <f t="shared" si="0"/>
         <v>BA</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <v>3882</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43">
+      <c r="H11" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>02 dia, 00 horas, 31 minutos, 30 segundos</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="21">
+        <f t="shared" si="2"/>
+        <v>11657.806999999999</v>
+      </c>
+      <c r="K11" s="66">
         <v>33308.019999999997</v>
       </c>
-    </row>
-    <row r="12" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="40">
+      <c r="L11" s="74">
+        <f t="shared" si="3"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="19">
         <v>46186</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="19">
         <v>46198</v>
       </c>
-      <c r="D12" s="11">
-        <f t="shared" si="1"/>
+      <c r="D12" s="10">
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="11" t="str">
+      <c r="F12" s="10" t="str">
         <f t="shared" si="0"/>
         <v>SP</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <v>916</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43">
+      <c r="H12" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>00 dia, 11 horas, 27 minutos, 00 segundos</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="21">
+        <f t="shared" si="2"/>
+        <v>3838.6485000000002</v>
+      </c>
+      <c r="K12" s="22">
         <v>8530.33</v>
       </c>
-    </row>
-    <row r="13" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="74">
+        <f t="shared" si="3"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="38" t="s">
+    <row r="14" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="E14" s="16" t="s">
+      <c r="C14" s="60"/>
+      <c r="E14" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="13"/>
-      <c r="H14" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="37"/>
-    </row>
-    <row r="15" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="26"/>
-      <c r="C15" s="27"/>
+      <c r="F14" s="12"/>
+      <c r="H14" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="58"/>
+    </row>
+    <row r="15" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="50"/>
+      <c r="C15" s="51"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="12"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="29"/>
-    </row>
-    <row r="16" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="24" t="s">
+      <c r="F15" s="11"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="53"/>
+    </row>
+    <row r="16" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="E16" s="18" t="s">
+      <c r="C16" s="49"/>
+      <c r="E16" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="13"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+      <c r="F16" s="12"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
     </row>
     <row r="17" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="53"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="12"/>
-      <c r="H17" s="36" t="s">
+      <c r="F17" s="11"/>
+      <c r="H17" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="37"/>
+      <c r="I17" s="58"/>
     </row>
     <row r="18" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="29"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="53"/>
     </row>
     <row r="19" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="23"/>
-      <c r="E19" s="16" t="s">
+      <c r="C19" s="47"/>
+      <c r="E19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="13"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
+      <c r="F19" s="12"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
     </row>
     <row r="20" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="25"/>
+      <c r="C20" s="49"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="12"/>
-      <c r="H20" s="36" t="s">
+      <c r="F20" s="11"/>
+      <c r="H20" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="37"/>
+      <c r="I20" s="58"/>
     </row>
     <row r="21" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="26"/>
-      <c r="C21" s="27"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="29"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="51"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="53"/>
     </row>
     <row r="22" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="E22" s="16" t="s">
+      <c r="C22" s="49"/>
+      <c r="E22" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13"/>
+      <c r="F22" s="12"/>
     </row>
     <row r="23" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="26"/>
-      <c r="C23" s="27"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="51"/>
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="2:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="20"/>
-      <c r="C24" s="21"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="12"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="45"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26"/>
@@ -2375,7 +2527,8 @@
       <c r="B33"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="H19:I19"/>
@@ -2399,7 +2552,7 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{E839BB19-5F09-4525-9529-897BA60ABD8A}">
       <formula1>"Guariroba,Jurupema,Taquaritinga,Vila Negri"</formula1>
     </dataValidation>
